--- a/resources/templates/standard/F1101-01.xlsx
+++ b/resources/templates/standard/F1101-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>신임 교육 계획서</t>
   </si>
@@ -696,11 +699,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -710,18 +715,18 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N1" s="4"/>
       <c r="O1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P1" s="4"/>
       <c r="Q1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R1" s="4"/>
     </row>
@@ -787,7 +792,7 @@
     </row>
     <row r="5" ht="21.95" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -798,7 +803,7 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -811,7 +816,7 @@
     </row>
     <row r="6" ht="21.95" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -822,7 +827,7 @@
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
@@ -835,7 +840,7 @@
     </row>
     <row r="7" ht="21.95" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -846,7 +851,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
@@ -859,7 +864,7 @@
     </row>
     <row r="8" ht="21.95" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -870,7 +875,7 @@
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
@@ -883,15 +888,15 @@
     </row>
     <row r="9" ht="29.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
@@ -900,12 +905,12 @@
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
@@ -1193,7 +1198,7 @@
     </row>
     <row r="24" ht="21.95" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -1255,7 +1260,7 @@
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
